--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2020_coquimbo.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:12</t>
+    <t xml:space="preserve">2026-09-24 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -552,19 +552,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>-0.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="3">
@@ -575,19 +575,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>-0.45</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="4">
@@ -598,19 +598,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>-0.2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="5">
@@ -621,19 +621,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="6">
@@ -644,19 +644,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.34</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
@@ -667,19 +667,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
@@ -690,16 +690,16 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-0.07</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.45</v>
@@ -716,13 +716,13 @@
         <v>-0.51</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>-0.08</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>-0.43</v>
@@ -736,19 +736,19 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="11">
@@ -759,19 +759,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>-0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="12">
@@ -782,19 +782,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13">
@@ -805,19 +805,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.22</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="14">
@@ -828,19 +828,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="15">
@@ -851,19 +851,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="16">
@@ -877,13 +877,13 @@
         <v>-0.1</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.11</v>
@@ -897,19 +897,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-0.12</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="18">
@@ -923,13 +923,13 @@
         <v>-0.71</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-0.63</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.08</v>
@@ -943,19 +943,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="20">
@@ -966,19 +966,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="21">
@@ -989,16 +989,16 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.51</v>
